--- a/apps/web/public/atlaslog-program-template.xlsx
+++ b/apps/web/public/atlaslog-program-template.xlsx
@@ -903,7 +903,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -929,9 +929,17 @@
         <v>Squat · Bench · Deadlift</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>program_type</v>
+      </c>
+      <c r="B4" t="str">
+        <v>powerlifting</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/apps/web/public/atlaslog-program-template.xlsx
+++ b/apps/web/public/atlaslog-program-template.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Program" sheetId="1" r:id="rId1"/>
-    <sheet name="Meta" sheetId="2" r:id="rId2"/>
+    <sheet name="Template" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,44 +397,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L20"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" customWidth="1"/>
+    <col min="8" max="8" width="7.83203125" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" customWidth="1"/>
+    <col min="10" max="10" width="6.83203125" customWidth="1"/>
+    <col min="11" max="11" width="6.83203125" customWidth="1"/>
+    <col min="12" max="12" width="34.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>week</v>
+        <v>Week</v>
       </c>
       <c r="B1" t="str">
-        <v>phase</v>
+        <v>Phase</v>
       </c>
       <c r="C1" t="str">
-        <v>day_of_week</v>
+        <v>Day</v>
       </c>
       <c r="D1" t="str">
-        <v>focus</v>
+        <v>Lift</v>
       </c>
       <c r="E1" t="str">
-        <v>exercise_name</v>
+        <v>Variant</v>
       </c>
       <c r="F1" t="str">
-        <v>exercise_id</v>
+        <v>Prescription</v>
       </c>
       <c r="G1" t="str">
-        <v>type</v>
+        <v>Sets</v>
       </c>
       <c r="H1" t="str">
-        <v>sets</v>
+        <v>Reps</v>
       </c>
       <c r="I1" t="str">
-        <v>reps</v>
+        <v>PCT</v>
       </c>
       <c r="J1" t="str">
-        <v>pct</v>
+        <v>RPE</v>
       </c>
       <c r="K1" t="str">
-        <v>rpe</v>
+        <v>Type</v>
       </c>
       <c r="L1" t="str">
-        <v>note</v>
+        <v>Notes</v>
       </c>
     </row>
     <row r="2">
@@ -449,31 +462,31 @@
         <v>Mon</v>
       </c>
       <c r="D2" t="str">
-        <v>Squat Focus</v>
+        <v>Squat</v>
       </c>
       <c r="E2" t="str">
-        <v>Back Squat</v>
+        <v>Competition</v>
       </c>
       <c r="F2" t="str">
-        <v>squat</v>
-      </c>
-      <c r="G2" t="str">
-        <v>main</v>
+        <v>Top set</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="J2">
-        <v>0.75</v>
+        <v>7</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>Work</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>คุมจังหวะ 2-0-1</v>
       </c>
     </row>
     <row r="3">
@@ -487,31 +500,31 @@
         <v>Mon</v>
       </c>
       <c r="D3" t="str">
-        <v>Squat Focus</v>
+        <v>Squat</v>
       </c>
       <c r="E3" t="str">
-        <v>Leg Press</v>
+        <v>Competition</v>
       </c>
       <c r="F3" t="str">
-        <v>leg_press</v>
-      </c>
-      <c r="G3" t="str">
-        <v>accessory</v>
+        <v>Back-off</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>10</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3">
-        <v>8</v>
+        <v>0.7</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Work</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>โฟกัสฟอร์ม</v>
       </c>
     </row>
     <row r="4">
@@ -522,34 +535,34 @@
         <v>Accumulation</v>
       </c>
       <c r="C4" t="str">
-        <v>Wed</v>
+        <v>Mon</v>
       </c>
       <c r="D4" t="str">
-        <v>Bench Focus</v>
+        <v>Deadlift</v>
       </c>
       <c r="E4" t="str">
-        <v>Bench Press</v>
+        <v>Volume</v>
       </c>
       <c r="F4" t="str">
-        <v>bench</v>
-      </c>
-      <c r="G4" t="str">
-        <v>main</v>
+        <v>Work sets</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J4">
-        <v>0.72</v>
+        <v>7</v>
       </c>
       <c r="K4" t="str">
+        <v>Work</v>
+      </c>
+      <c r="L4" t="str">
         <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>เน้น leg drive</v>
       </c>
     </row>
     <row r="5">
@@ -560,34 +573,34 @@
         <v>Accumulation</v>
       </c>
       <c r="C5" t="str">
-        <v>Wed</v>
+        <v>Tue</v>
       </c>
       <c r="D5" t="str">
-        <v>Bench Focus</v>
+        <v>Bench</v>
       </c>
       <c r="E5" t="str">
-        <v>Barbell Row</v>
+        <v>Competition</v>
       </c>
       <c r="F5" t="str">
-        <v>barbell_row</v>
-      </c>
-      <c r="G5" t="str">
-        <v>accessory</v>
+        <v>Top set</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5">
-        <v>8</v>
+        <v>0.75</v>
+      </c>
+      <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Work</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>Pause 1 วิ</v>
       </c>
     </row>
     <row r="6">
@@ -598,31 +611,31 @@
         <v>Accumulation</v>
       </c>
       <c r="C6" t="str">
-        <v>Fri</v>
+        <v>Tue</v>
       </c>
       <c r="D6" t="str">
-        <v>Deadlift Focus</v>
+        <v>Bench</v>
       </c>
       <c r="E6" t="str">
-        <v>Deadlift</v>
+        <v>Competition</v>
       </c>
       <c r="F6" t="str">
-        <v>deadlift</v>
-      </c>
-      <c r="G6" t="str">
-        <v>main</v>
+        <v>Back-off</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J6">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>Work</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -636,69 +649,69 @@
         <v>Accumulation</v>
       </c>
       <c r="C7" t="str">
-        <v>Fri</v>
+        <v>Thu</v>
       </c>
       <c r="D7" t="str">
-        <v>Deadlift Focus</v>
+        <v>Bench</v>
       </c>
       <c r="E7" t="str">
-        <v>Romanian Deadlift</v>
+        <v>Volume</v>
       </c>
       <c r="F7" t="str">
-        <v>rdl</v>
-      </c>
-      <c r="G7" t="str">
-        <v>accessory</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
+        <v>AMRAP set</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="str">
+        <v>AMRAP</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>0.65</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
-      <c r="K7">
-        <v>7</v>
+      <c r="K7" t="str">
+        <v>Work</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>เซ็ตสุดท้ายลากให้สุด</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="str">
-        <v>Intensification</v>
+        <v>Accumulation</v>
       </c>
       <c r="C8" t="str">
-        <v>Mon</v>
+        <v>Fri</v>
       </c>
       <c r="D8" t="str">
-        <v>Squat Focus</v>
+        <v>Deadlift</v>
       </c>
       <c r="E8" t="str">
-        <v>Back Squat</v>
+        <v>Competition</v>
       </c>
       <c r="F8" t="str">
-        <v>squat</v>
-      </c>
-      <c r="G8" t="str">
-        <v>main</v>
+        <v>Top set</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="J8">
-        <v>0.82</v>
+        <v>7</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>Work</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -706,37 +719,37 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="str">
-        <v>Intensification</v>
+        <v>Accumulation</v>
       </c>
       <c r="C9" t="str">
-        <v>Wed</v>
+        <v>Fri</v>
       </c>
       <c r="D9" t="str">
-        <v>Bench Focus</v>
+        <v>Squat</v>
       </c>
       <c r="E9" t="str">
-        <v>Bench Press</v>
+        <v>Volume</v>
       </c>
       <c r="F9" t="str">
-        <v>bench</v>
-      </c>
-      <c r="G9" t="str">
-        <v>main</v>
+        <v>Work sets</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J9">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>Work</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -747,34 +760,34 @@
         <v>2</v>
       </c>
       <c r="B10" t="str">
-        <v>Intensification</v>
+        <v>Accumulation</v>
       </c>
       <c r="C10" t="str">
-        <v>Fri</v>
+        <v>Mon</v>
       </c>
       <c r="D10" t="str">
-        <v>Deadlift Focus</v>
+        <v>Squat</v>
       </c>
       <c r="E10" t="str">
-        <v>Deadlift</v>
+        <v>Competition</v>
       </c>
       <c r="F10" t="str">
-        <v>deadlift</v>
-      </c>
-      <c r="G10" t="str">
-        <v>main</v>
+        <v>Top set</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>0.775</v>
       </c>
       <c r="J10">
-        <v>0.85</v>
+        <v>7.5</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>Work</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -782,75 +795,75 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="str">
-        <v>Peaking</v>
+        <v>Accumulation</v>
       </c>
       <c r="C11" t="str">
         <v>Mon</v>
       </c>
       <c r="D11" t="str">
-        <v>Squat Focus</v>
+        <v>Squat</v>
       </c>
       <c r="E11" t="str">
-        <v>Back Squat</v>
+        <v>Competition</v>
       </c>
       <c r="F11" t="str">
-        <v>squat</v>
-      </c>
-      <c r="G11" t="str">
-        <v>main</v>
+        <v>Back-off</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="str">
-        <v>AMRAP</v>
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>0.725</v>
       </c>
       <c r="J11">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="K11" t="str">
+        <v>Work</v>
+      </c>
+      <c r="L11" t="str">
         <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>test single</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="str">
-        <v>Peaking</v>
+        <v>Accumulation</v>
       </c>
       <c r="C12" t="str">
-        <v>Wed</v>
+        <v>Mon</v>
       </c>
       <c r="D12" t="str">
-        <v>Bench Focus</v>
+        <v>Deadlift</v>
       </c>
       <c r="E12" t="str">
-        <v>Bench Press</v>
+        <v>Volume</v>
       </c>
       <c r="F12" t="str">
-        <v>bench</v>
-      </c>
-      <c r="G12" t="str">
-        <v>main</v>
+        <v>Work sets</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" t="str">
-        <v>AMRAP</v>
+        <v>6</v>
+      </c>
+      <c r="I12">
+        <v>0.7</v>
       </c>
       <c r="J12">
-        <v>0.88</v>
+        <v>7.5</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>Work</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -858,88 +871,311 @@
     </row>
     <row r="13">
       <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Accumulation</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Bench</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Competition</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Top set</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>0.775</v>
+      </c>
+      <c r="J13">
+        <v>7.5</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Work</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Pause 1 วิ</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Accumulation</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Bench</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Competition</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Back-off</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>0.725</v>
+      </c>
+      <c r="J14">
+        <v>6.5</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Work</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Accumulation</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Bench</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Volume</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Work sets</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>8</v>
+      </c>
+      <c r="I15">
+        <v>0.7</v>
+      </c>
+      <c r="J15">
+        <v>7.5</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Work</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Accumulation</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Deadlift</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Competition</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Top set</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>0.775</v>
+      </c>
+      <c r="J16">
+        <v>7.5</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Work</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Accumulation</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Squat</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Volume</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Work sets</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>6</v>
+      </c>
+      <c r="I17">
+        <v>0.725</v>
+      </c>
+      <c r="J17">
+        <v>7.5</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Work</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
         <v>3</v>
       </c>
-      <c r="B13" t="str">
-        <v>Peaking</v>
-      </c>
-      <c r="C13" t="str">
+      <c r="B18" t="str">
+        <v>Taper/Test</v>
+      </c>
+      <c r="C18" t="str">
         <v>Fri</v>
       </c>
-      <c r="D13" t="str">
-        <v>Deadlift Focus</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Deadlift</v>
-      </c>
-      <c r="F13" t="str">
-        <v>deadlift</v>
-      </c>
-      <c r="G13" t="str">
-        <v>main</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>0.92</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
+      <c r="D18" t="str">
+        <v>Squat</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Competition</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Attempt 1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>0.9</v>
+      </c>
+      <c r="J18">
+        <v>8</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Test</v>
+      </c>
+      <c r="L18" t="str">
+        <v>1st attempt</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Taper/Test</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Squat</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Competition</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Attempt 2</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>0.97</v>
+      </c>
+      <c r="J19">
+        <v>9</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Test</v>
+      </c>
+      <c r="L19" t="str">
+        <v>2nd attempt</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Taper/Test</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Squat</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Competition</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Attempt 3</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1.02</v>
+      </c>
+      <c r="J20">
+        <v>9.5</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Test</v>
+      </c>
+      <c r="L20" t="str">
+        <v>3rd attempt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>My 3 Week Peak</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>description</v>
-      </c>
-      <c r="B2" t="str">
-        <v>โปรแกรมตัวอย่างสำหรับ intermediate lifter (SBD)</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>focus</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Squat · Bench · Deadlift</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>program_type</v>
-      </c>
-      <c r="B4" t="str">
-        <v>powerlifting</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
   </ignoredErrors>
 </worksheet>
 </file>